--- a/분데스리가_2026-2027.xlsx
+++ b/분데스리가_2026-2027.xlsx
@@ -545,79 +545,79 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>08.30</t>
+          <t>08.29</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>03:30</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>아우크스부르크</t>
+          <t>바이에른 뮌헨</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
       <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>샬케</t>
+          <t>VfB 슈투트가르트</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>10.00</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
           <t>2.00</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Q2" s="2" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
       <c r="R2" s="2" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="T2" s="2" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.93</t>
         </is>
       </c>
     </row>
@@ -639,7 +639,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>08.30</t>
+          <t>08.29</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -649,69 +649,69 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>도르트문트</t>
+          <t>엘버스베르크</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr"/>
       <c r="I3" s="2" t="inlineStr"/>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>함부르크 SV</t>
+          <t>레버쿠젠</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>6.00</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>5.50</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>7.50</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3/3.5</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="R3" s="2" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="S3" s="2" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>-1/1.5</t>
         </is>
       </c>
       <c r="T3" s="2" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.93</t>
         </is>
       </c>
     </row>
@@ -733,7 +733,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>08.30</t>
+          <t>08.29</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -743,69 +743,69 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>엘버스베르크</t>
+          <t>쾰른</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>레버쿠젠</t>
+          <t>호펜하임</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3/3.5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>-1/1.5</t>
+          <t>0/-0.5</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.80</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>08.30</t>
+          <t>08.29</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -837,69 +837,69 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>쾰른</t>
+          <t>마인츠</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
       <c r="I5" s="2" t="inlineStr"/>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>호펜하임</t>
+          <t>파더보른</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>2.5/3</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
           <t>2.05</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="R5" s="2" t="inlineStr">
         <is>
           <t>1.80</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>0.5/1</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
         <is>
           <t>2.05</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>0/-0.5</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>1.80</t>
         </is>
       </c>
     </row>
@@ -921,7 +921,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>08.30</t>
+          <t>08.29</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -931,69 +931,69 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>프라이부르크</t>
+          <t>RB 라이프치히</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>18</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
       <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>베르더 브레멘</t>
+          <t>묀헨글라트바흐</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>6.00</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2.5/3</t>
+          <t>3/3.5</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>2.05</t>
         </is>
       </c>
     </row>
@@ -1015,7 +1015,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>08.30</t>
+          <t>08.29</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1025,44 +1025,44 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>마인츠</t>
+          <t>우니온 베를린</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>15</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr"/>
       <c r="I7" s="2" t="inlineStr"/>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>파더보른</t>
+          <t>프랑크푸르트</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1072,22 +1072,22 @@
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>0.5/1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>1.95</t>
         </is>
       </c>
     </row>
@@ -1114,74 +1114,74 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>01:30</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>RB 라이프치히</t>
+          <t>도르트문트</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr"/>
       <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>함부르크 SV</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>7.50</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>묀헨글라트바흐</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>1.50</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>6.00</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>3/3.5</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>1.95</t>
         </is>
       </c>
     </row>
@@ -1213,39 +1213,39 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>우니온 베를린</t>
+          <t>프라이부르크</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr"/>
       <c r="I9" s="2" t="inlineStr"/>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>프랑크푸르트</t>
+          <t>베르더 브레멘</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
@@ -1265,17 +1265,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
           <t>1.90</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>1.95</t>
         </is>
       </c>
     </row>
@@ -1302,44 +1302,44 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>03:30</t>
+          <t>00:30</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>바이에른 뮌헨</t>
+          <t>아우크스부르크</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr"/>
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>VfB 슈투트가르트</t>
+          <t>샬케</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>10.00</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1359,17 +1359,17 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.83</t>
         </is>
       </c>
     </row>
